--- a/data/trans_bre/P36B08_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 12,56</t>
+          <t>5,37; 12,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,21</t>
+          <t>3,96; 11,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,99</t>
+          <t>-1,31; 7,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 4,62</t>
+          <t>-1,01; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 20,34</t>
+          <t>8,04; 20,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 16,05</t>
+          <t>5,32; 16,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 9,44</t>
+          <t>-1,66; 9,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,09</t>
+          <t>-1,05; 4,41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,34</t>
+          <t>4,71; 11,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,84</t>
+          <t>5,22; 11,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,78</t>
+          <t>2,86; 8,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,04</t>
+          <t>0,59; 3,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 18,77</t>
+          <t>7,25; 18,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,28; 15,94</t>
+          <t>7,42; 16,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 12,94</t>
+          <t>4,09; 13,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,31</t>
+          <t>0,6; 3,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-0,34%</t>
+          <t>-0,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 10,65</t>
+          <t>-1,34; 10,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 15,01</t>
+          <t>4,24; 14,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 8,49</t>
+          <t>-1,39; 8,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,63</t>
+          <t>-2,05; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 16,77</t>
+          <t>-1,91; 16,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 20,45</t>
+          <t>5,44; 20,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 11,2</t>
+          <t>-1,78; 11,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,72</t>
+          <t>-2,1; 2,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,3</t>
+          <t>5,65; 10,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,44</t>
+          <t>6,51; 10,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,18</t>
+          <t>3,1; 7,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,77</t>
+          <t>0,36; 2,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 16,75</t>
+          <t>8,72; 16,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,96</t>
+          <t>9,02; 15,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,07</t>
+          <t>4,22; 10,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,96</t>
+          <t>0,38; 2,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P36B08_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
